--- a/Codelist Excel Files and Conversion Templates to XML/consequenceClass.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/consequenceClass.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes naming the consequence or reliability class governing a rigid inclusion design. Used for the value of the consequenceClass property of diggs:RISystemBasis. RI_Design_Parameter_Analysis.md Group A row 10 flags that several national schemes (ASIRI's domain classification, EBGEO's load case) occupy this same conceptual slot but are not directly interchangeable with the Eurocode classes or with each other, and that the exact ASIRI domain definitions could not be verified from open sources. This list is deliberately EC7/EN 1990-sourced only, pending SME confirmation of the other schemes - see docs/build/S9/NOTES.md.</t>
+          <t>Codes naming the consequence or reliability class governing a rigid inclusion design. Used for the value of the consequenceClass property of diggs:RIProgramBasis. RI_Design_Parameter_Analysis.md Group A row 10 flags that several national schemes (ASIRI's domain classification, EBGEO's load case) occupy this same conceptual slot but are not directly interchangeable with the Eurocode classes or with each other, and that the exact ASIRI domain definitions could not be verified from open sources. This list is deliberately EC7/EN 1990-sourced only, pending SME confirmation of the other schemes - see docs/build/S9/NOTES.md.</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:consequenceClass</t>
+          <t>//diggs:RIProgramBasis/diggs:consequenceClass</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:consequenceClass</t>
+          <t>//diggs:RIProgramBasis/diggs:consequenceClass</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:consequenceClass</t>
+          <t>//diggs:RIProgramBasis/diggs:consequenceClass</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/consequenceClass.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/consequenceClass.xlsx
@@ -980,12 +980,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>DIGGS Rigid Inclusion Consequence Class Codelist Definitions</t>
+          <t>DIGGS Consequence Class Codelist Definitions</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes naming the consequence or reliability class governing a rigid inclusion design. Used for the value of the consequenceClass property of diggs:RIProgramBasis. RI_Design_Parameter_Analysis.md Group A row 10 flags that several national schemes (ASIRI's domain classification, EBGEO's load case) occupy this same conceptual slot but are not directly interchangeable with the Eurocode classes or with each other, and that the exact ASIRI domain definitions could not be verified from open sources. This list is deliberately EC7/EN 1990-sourced only, pending SME confirmation of the other schemes - see docs/build/S9/NOTES.md.</t>
+          <t>Codes naming the consequence or reliability class governing a design. Used for the value of the consequenceClass property of diggs:AbstractProgramBasis, and so available on any concrete program basis rather than only diggs:RIProgramBasis, which is where the property was originally declared (S9) before it was moved to the abstract base at D10 as a premise generic to any designed program. RI_Design_Parameter_Analysis.md Group A row 10 flags that several national schemes (ASIRI's domain classification, EBGEO's load case) occupy this same conceptual slot but are not directly interchangeable with the Eurocode classes or with each other, and that the exact ASIRI domain definitions could not be verified from open sources. This list is deliberately EC7/EN 1990-sourced only, pending SME confirmation of the other schemes - see docs/build/S9/NOTES.md and docs/build/PR3/NOTES.md.</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>//diggs:RIProgramBasis/diggs:consequenceClass</t>
+          <t>//diggs:consequenceClass</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>//diggs:RIProgramBasis/diggs:consequenceClass</t>
+          <t>//diggs:consequenceClass</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>//diggs:RIProgramBasis/diggs:consequenceClass</t>
+          <t>//diggs:consequenceClass</t>
         </is>
       </c>
     </row>
